--- a/temp/diversos/Prensas.xlsx
+++ b/temp/diversos/Prensas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="114">
   <si>
     <t>ABRAÇADEIRA UV PRETA 202X3,7</t>
   </si>
@@ -61,9 +61,6 @@
     <t>BARRA CHATA 1.1/4" X 1/8"</t>
   </si>
   <si>
-    <t>BASE AGL - AL100R - BRUTO</t>
-  </si>
-  <si>
     <t>BASE AGL - MINI - A. EXT. - BRUTO</t>
   </si>
   <si>
@@ -88,6 +85,9 @@
     <t>BOBINA AÇO GALV. SAE1006 - 2,3 X 40MM</t>
   </si>
   <si>
+    <t>BOBINA AÇO SAE1006 - 1,2 X 133,5MM</t>
+  </si>
+  <si>
     <t>BOBINA AÇO SAE1006 - 1,2 X 147MM</t>
   </si>
   <si>
@@ -217,9 +217,6 @@
     <t>COPO DE FREIO DESLIZANTE</t>
   </si>
   <si>
-    <t>CRUZETA DO MANCAL</t>
-  </si>
-  <si>
     <t>CZN 1,95 x 1200 N7008 ZC Z100 CT</t>
   </si>
   <si>
@@ -256,16 +253,16 @@
     <t>FUNDO PRETO PORTEIRO ELETRÔNICO COLETIVO 44 E 48 PONTOS</t>
   </si>
   <si>
+    <t>NI-RT SAE-060 AGL P24 04P</t>
+  </si>
+  <si>
     <t>NI-RT SAE-060 AGL P27,6 04P</t>
   </si>
   <si>
-    <t>NI-RT SAE-060 AGL P33 04P</t>
-  </si>
-  <si>
     <t>NI-RT SAE-060 AGL P80 04P</t>
   </si>
   <si>
-    <t>PARAFUSO PAN PLASTIC PHS 3,5X14MM ZI</t>
+    <t>PARAFUSO PAN CRUZ 3,5MMX14MM (FABR. AGL) - ZINCADO</t>
   </si>
   <si>
     <t>PARAFUSO PLASTIC PAN PHS 5 X 25MM - BRUTO (PROD)</t>
@@ -457,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" width="7.33203125" min="1" max="1"/>
@@ -793,7 +790,7 @@
     </row>
     <row r="11" customHeight="1" ht="15" spans="1:10">
       <c r="A11" s="1" t="n">
-        <v>701003</v>
+        <v>701004</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>16</v>
@@ -808,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>13897</v>
+        <v>317</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -825,7 +822,7 @@
     </row>
     <row r="12" customHeight="1" ht="15" spans="1:10">
       <c r="A12" s="1" t="n">
-        <v>701004</v>
+        <v>801011</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>17</v>
@@ -840,7 +837,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>317</v>
+        <v>1</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -857,7 +854,7 @@
     </row>
     <row r="13" customHeight="1" ht="15" spans="1:10">
       <c r="A13" s="1" t="n">
-        <v>801011</v>
+        <v>701117</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>18</v>
@@ -872,7 +869,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -889,7 +886,7 @@
     </row>
     <row r="14" customHeight="1" ht="15" spans="1:10">
       <c r="A14" s="1" t="n">
-        <v>701117</v>
+        <v>701011</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>19</v>
@@ -904,7 +901,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>214</v>
+        <v>2708</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -921,7 +918,7 @@
     </row>
     <row r="15" customHeight="1" ht="15" spans="1:10">
       <c r="A15" s="1" t="n">
-        <v>701011</v>
+        <v>701014</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>20</v>
@@ -936,7 +933,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2708</v>
+        <v>1662</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -953,22 +950,22 @@
     </row>
     <row r="16" customHeight="1" ht="15" spans="1:10">
       <c r="A16" s="1" t="n">
-        <v>701014</v>
+        <v>201134</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1662</v>
+        <v>14466.896</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0</v>
@@ -985,7 +982,7 @@
     </row>
     <row r="17" customHeight="1" ht="15" spans="1:10">
       <c r="A17" s="1" t="n">
-        <v>201134</v>
+        <v>201149</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>22</v>
@@ -1000,7 +997,7 @@
         <v>7</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>14466.896</v>
+        <v>2790.64</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0</v>
@@ -1017,7 +1014,7 @@
     </row>
     <row r="18" customHeight="1" ht="15" spans="1:10">
       <c r="A18" s="1" t="n">
-        <v>201149</v>
+        <v>208008</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>23</v>
@@ -1032,7 +1029,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2790.64</v>
+        <v>445</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0</v>
@@ -1049,7 +1046,7 @@
     </row>
     <row r="19" customHeight="1" ht="15" spans="1:10">
       <c r="A19" s="1" t="n">
-        <v>208008</v>
+        <v>201002</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>24</v>
@@ -1064,7 +1061,7 @@
         <v>7</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>445</v>
+        <v>5840</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
@@ -1096,7 +1093,7 @@
         <v>7</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>8222.94</v>
+        <v>11417.94</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0</v>
@@ -1224,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4080</v>
+        <v>8010</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0</v>
@@ -1256,7 +1253,7 @@
         <v>7</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>7120.768</v>
+        <v>6905.28</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
@@ -1288,7 +1285,7 @@
         <v>7</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5158.404948</v>
+        <v>5102.904948</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>0</v>
@@ -1736,7 +1733,7 @@
         <v>46</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>15043</v>
+        <v>14051</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -1992,7 +1989,7 @@
         <v>3</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1294.625</v>
+        <v>1274.46116</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -2152,7 +2149,7 @@
         <v>3</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>212.75</v>
+        <v>1412.77</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0</v>
@@ -2425,22 +2422,22 @@
     </row>
     <row r="62" customHeight="1" ht="15" spans="1:10">
       <c r="A62" s="1" t="n">
-        <v>813280</v>
+        <v>201073</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>30</v>
+        <v>6374.36056</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>0</v>
@@ -2457,22 +2454,22 @@
     </row>
     <row r="63" customHeight="1" ht="15" spans="1:10">
       <c r="A63" s="1" t="n">
-        <v>201073</v>
+        <v>813353</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>1347.36056</v>
+        <v>64</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0</v>
@@ -2489,13 +2486,13 @@
     </row>
     <row r="64" customHeight="1" ht="15" spans="1:10">
       <c r="A64" s="1" t="n">
-        <v>813353</v>
+        <v>811306</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>2</v>
@@ -2504,7 +2501,7 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>64</v>
+        <v>2500</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -2521,13 +2518,13 @@
     </row>
     <row r="65" customHeight="1" ht="15" spans="1:10">
       <c r="A65" s="1" t="n">
-        <v>811306</v>
+        <v>811307</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>2</v>
@@ -2536,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>2500</v>
+        <v>1.628</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0</v>
@@ -2553,22 +2550,22 @@
     </row>
     <row r="66" customHeight="1" ht="15" spans="1:10">
       <c r="A66" s="1" t="n">
-        <v>811307</v>
+        <v>202084</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1.628</v>
+        <v>11.68</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0</v>
@@ -2585,22 +2582,22 @@
     </row>
     <row r="67" customHeight="1" ht="15" spans="1:10">
       <c r="A67" s="1" t="n">
-        <v>202084</v>
+        <v>807045</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>11.68</v>
+        <v>292</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -2617,7 +2614,7 @@
     </row>
     <row r="68" customHeight="1" ht="15" spans="1:10">
       <c r="A68" s="1" t="n">
-        <v>807045</v>
+        <v>807001</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>74</v>
@@ -2632,7 +2629,7 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>292</v>
+        <v>61</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0</v>
@@ -2649,7 +2646,7 @@
     </row>
     <row r="69" customHeight="1" ht="15" spans="1:10">
       <c r="A69" s="1" t="n">
-        <v>807001</v>
+        <v>807008</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>75</v>
@@ -2664,7 +2661,7 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0</v>
@@ -2681,7 +2678,7 @@
     </row>
     <row r="70" customHeight="1" ht="15" spans="1:10">
       <c r="A70" s="1" t="n">
-        <v>807008</v>
+        <v>807004</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>76</v>
@@ -2696,7 +2693,7 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>0</v>
@@ -2713,7 +2710,7 @@
     </row>
     <row r="71" customHeight="1" ht="15" spans="1:10">
       <c r="A71" s="1" t="n">
-        <v>807004</v>
+        <v>807012</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>77</v>
@@ -2728,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>169</v>
+        <v>86</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0</v>
@@ -2745,7 +2742,7 @@
     </row>
     <row r="72" customHeight="1" ht="15" spans="1:10">
       <c r="A72" s="1" t="n">
-        <v>807012</v>
+        <v>807013</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>78</v>
@@ -2760,7 +2757,7 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="G72" s="3" t="n">
         <v>0</v>
@@ -2777,7 +2774,7 @@
     </row>
     <row r="73" customHeight="1" ht="15" spans="1:10">
       <c r="A73" s="1" t="n">
-        <v>807013</v>
+        <v>807195</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>79</v>
@@ -2792,7 +2789,7 @@
         <v>3</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>0</v>
@@ -2809,7 +2806,7 @@
     </row>
     <row r="74" customHeight="1" ht="15" spans="1:10">
       <c r="A74" s="1" t="n">
-        <v>807195</v>
+        <v>813448</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>80</v>
@@ -2824,7 +2821,7 @@
         <v>3</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>1</v>
+        <v>2650</v>
       </c>
       <c r="G74" s="3" t="n">
         <v>0</v>
@@ -2856,7 +2853,7 @@
         <v>3</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>3024</v>
+        <v>2400</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
@@ -2873,7 +2870,7 @@
     </row>
     <row r="76" customHeight="1" ht="15" spans="1:10">
       <c r="A76" s="1" t="n">
-        <v>813445</v>
+        <v>813449</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>82</v>
@@ -2888,7 +2885,7 @@
         <v>3</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>3003</v>
+        <v>256</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0</v>
@@ -2905,7 +2902,7 @@
     </row>
     <row r="77" customHeight="1" ht="15" spans="1:10">
       <c r="A77" s="1" t="n">
-        <v>813449</v>
+        <v>401136</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>83</v>
@@ -2920,7 +2917,7 @@
         <v>3</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>256</v>
+        <v>55582</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0</v>
@@ -2937,7 +2934,7 @@
     </row>
     <row r="78" customHeight="1" ht="15" spans="1:10">
       <c r="A78" s="1" t="n">
-        <v>401169</v>
+        <v>707038</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>84</v>
@@ -2952,7 +2949,7 @@
         <v>3</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>126891</v>
+        <v>44637</v>
       </c>
       <c r="G78" s="3" t="n">
         <v>0</v>
@@ -2969,7 +2966,7 @@
     </row>
     <row r="79" customHeight="1" ht="15" spans="1:10">
       <c r="A79" s="1" t="n">
-        <v>707038</v>
+        <v>701050</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>85</v>
@@ -2984,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>44637</v>
+        <v>16720</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0</v>
@@ -3001,22 +2998,22 @@
     </row>
     <row r="80" customHeight="1" ht="15" spans="1:10">
       <c r="A80" s="1" t="n">
-        <v>701050</v>
+        <v>201099</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>16720</v>
+        <v>691.183</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>0</v>
@@ -3033,7 +3030,7 @@
     </row>
     <row r="81" customHeight="1" ht="15" spans="1:10">
       <c r="A81" s="1" t="n">
-        <v>201099</v>
+        <v>201089</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>87</v>
@@ -3048,7 +3045,7 @@
         <v>7</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>691.183</v>
+        <v>274.082</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0</v>
@@ -3065,7 +3062,7 @@
     </row>
     <row r="82" customHeight="1" ht="15" spans="1:10">
       <c r="A82" s="1" t="n">
-        <v>201089</v>
+        <v>201040</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>88</v>
@@ -3080,7 +3077,7 @@
         <v>7</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>274.082</v>
+        <v>235.98</v>
       </c>
       <c r="G82" s="3" t="n">
         <v>0</v>
@@ -3097,7 +3094,7 @@
     </row>
     <row r="83" customHeight="1" ht="15" spans="1:10">
       <c r="A83" s="1" t="n">
-        <v>201040</v>
+        <v>201056</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>89</v>
@@ -3112,7 +3109,7 @@
         <v>7</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>254.134</v>
+        <v>658.308</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>0</v>
@@ -3129,7 +3126,7 @@
     </row>
     <row r="84" customHeight="1" ht="15" spans="1:10">
       <c r="A84" s="1" t="n">
-        <v>201056</v>
+        <v>201057</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>90</v>
@@ -3144,7 +3141,7 @@
         <v>7</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>658.308</v>
+        <v>107.69</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>0</v>
@@ -3161,7 +3158,7 @@
     </row>
     <row r="85" customHeight="1" ht="15" spans="1:10">
       <c r="A85" s="1" t="n">
-        <v>201057</v>
+        <v>201095</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>91</v>
@@ -3176,7 +3173,7 @@
         <v>7</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>107.69</v>
+        <v>233.362436</v>
       </c>
       <c r="G85" s="3" t="n">
         <v>0</v>
@@ -3193,7 +3190,7 @@
     </row>
     <row r="86" customHeight="1" ht="15" spans="1:10">
       <c r="A86" s="1" t="n">
-        <v>201095</v>
+        <v>201035</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>92</v>
@@ -3205,10 +3202,10 @@
         <v>6</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>233.362436</v>
+        <v>570.454147</v>
       </c>
       <c r="G86" s="3" t="n">
         <v>0</v>
@@ -3225,22 +3222,22 @@
     </row>
     <row r="87" customHeight="1" ht="15" spans="1:10">
       <c r="A87" s="1" t="n">
-        <v>201035</v>
+        <v>708014</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>570.454147</v>
+        <v>36271</v>
       </c>
       <c r="G87" s="3" t="n">
         <v>0</v>
@@ -3257,7 +3254,7 @@
     </row>
     <row r="88" customHeight="1" ht="15" spans="1:10">
       <c r="A88" s="1" t="n">
-        <v>708014</v>
+        <v>813286</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>94</v>
@@ -3272,7 +3269,7 @@
         <v>3</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>31271</v>
+        <v>6843</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>0</v>
@@ -3289,7 +3286,7 @@
     </row>
     <row r="89" customHeight="1" ht="15" spans="1:10">
       <c r="A89" s="1" t="n">
-        <v>813286</v>
+        <v>708002</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>95</v>
@@ -3304,7 +3301,7 @@
         <v>3</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>6843</v>
+        <v>42074</v>
       </c>
       <c r="G89" s="3" t="n">
         <v>0</v>
@@ -3321,7 +3318,7 @@
     </row>
     <row r="90" customHeight="1" ht="15" spans="1:10">
       <c r="A90" s="1" t="n">
-        <v>708002</v>
+        <v>708001</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>96</v>
@@ -3336,7 +3333,7 @@
         <v>3</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>32906</v>
+        <v>25088</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>0</v>
@@ -3353,7 +3350,7 @@
     </row>
     <row r="91" customHeight="1" ht="15" spans="1:10">
       <c r="A91" s="1" t="n">
-        <v>708001</v>
+        <v>412069</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>97</v>
@@ -3368,7 +3365,7 @@
         <v>3</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>15920</v>
+        <v>4000</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0</v>
@@ -3385,7 +3382,7 @@
     </row>
     <row r="92" customHeight="1" ht="15" spans="1:10">
       <c r="A92" s="1" t="n">
-        <v>412069</v>
+        <v>412044</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>98</v>
@@ -3400,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -3417,7 +3414,7 @@
     </row>
     <row r="93" customHeight="1" ht="15" spans="1:10">
       <c r="A93" s="1" t="n">
-        <v>412044</v>
+        <v>412057</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>99</v>
@@ -3432,7 +3429,7 @@
         <v>3</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>5000</v>
+        <v>400</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
@@ -3449,7 +3446,7 @@
     </row>
     <row r="94" customHeight="1" ht="15" spans="1:10">
       <c r="A94" s="1" t="n">
-        <v>412057</v>
+        <v>412088</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>100</v>
@@ -3481,7 +3478,7 @@
     </row>
     <row r="95" customHeight="1" ht="15" spans="1:10">
       <c r="A95" s="1" t="n">
-        <v>412088</v>
+        <v>412093</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>101</v>
@@ -3496,7 +3493,7 @@
         <v>3</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>400</v>
+        <v>14000</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>0</v>
@@ -3513,7 +3510,7 @@
     </row>
     <row r="96" customHeight="1" ht="15" spans="1:10">
       <c r="A96" s="1" t="n">
-        <v>412093</v>
+        <v>412060</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>102</v>
@@ -3528,7 +3525,7 @@
         <v>3</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0</v>
@@ -3545,22 +3542,22 @@
     </row>
     <row r="97" customHeight="1" ht="15" spans="1:10">
       <c r="A97" s="1" t="n">
-        <v>412060</v>
+        <v>201117</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>2500</v>
+        <v>22809.378558</v>
       </c>
       <c r="G97" s="3" t="n">
         <v>0</v>
@@ -3577,7 +3574,7 @@
     </row>
     <row r="98" customHeight="1" ht="15" spans="1:10">
       <c r="A98" s="1" t="n">
-        <v>201117</v>
+        <v>201145</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>104</v>
@@ -3592,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>594.567186</v>
+        <v>3100</v>
       </c>
       <c r="G98" s="3" t="n">
         <v>0</v>
@@ -3609,7 +3606,7 @@
     </row>
     <row r="99" customHeight="1" ht="15" spans="1:10">
       <c r="A99" s="1" t="n">
-        <v>201145</v>
+        <v>201127</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>105</v>
@@ -3624,7 +3621,7 @@
         <v>7</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>3100</v>
+        <v>698.4205</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>0</v>
@@ -3641,7 +3638,7 @@
     </row>
     <row r="100" customHeight="1" ht="15" spans="1:10">
       <c r="A100" s="1" t="n">
-        <v>201127</v>
+        <v>201126</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>106</v>
@@ -3656,7 +3653,7 @@
         <v>7</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>698.4205</v>
+        <v>390</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -3673,7 +3670,7 @@
     </row>
     <row r="101" customHeight="1" ht="15" spans="1:10">
       <c r="A101" s="1" t="n">
-        <v>201126</v>
+        <v>201065</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>107</v>
@@ -3688,7 +3685,7 @@
         <v>7</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>390</v>
+        <v>2712.33918</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -3705,7 +3702,7 @@
     </row>
     <row r="102" customHeight="1" ht="15" spans="1:10">
       <c r="A102" s="1" t="n">
-        <v>201065</v>
+        <v>201066</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>108</v>
@@ -3720,7 +3717,7 @@
         <v>7</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>2712.33918</v>
+        <v>11871.06</v>
       </c>
       <c r="G102" s="3" t="n">
         <v>0</v>
@@ -3737,7 +3734,7 @@
     </row>
     <row r="103" customHeight="1" ht="15" spans="1:10">
       <c r="A103" s="1" t="n">
-        <v>201066</v>
+        <v>201051</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>109</v>
@@ -3752,7 +3749,7 @@
         <v>7</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>11871.06</v>
+        <v>3722</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>0</v>
@@ -3769,22 +3766,22 @@
     </row>
     <row r="104" customHeight="1" ht="15" spans="1:10">
       <c r="A104" s="1" t="n">
-        <v>201051</v>
+        <v>811762</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>3722</v>
+        <v>200</v>
       </c>
       <c r="G104" s="3" t="n">
         <v>0</v>
@@ -3801,7 +3798,7 @@
     </row>
     <row r="105" customHeight="1" ht="15" spans="1:10">
       <c r="A105" s="1" t="n">
-        <v>811762</v>
+        <v>801126</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>111</v>
@@ -3816,7 +3813,7 @@
         <v>3</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>0</v>
@@ -3833,7 +3830,7 @@
     </row>
     <row r="106" customHeight="1" ht="15" spans="1:10">
       <c r="A106" s="1" t="n">
-        <v>801126</v>
+        <v>813325</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>112</v>
@@ -3848,7 +3845,7 @@
         <v>3</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0</v>
@@ -3865,7 +3862,7 @@
     </row>
     <row r="107" customHeight="1" ht="15" spans="1:10">
       <c r="A107" s="1" t="n">
-        <v>813325</v>
+        <v>813324</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>113</v>
@@ -3880,7 +3877,7 @@
         <v>3</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>0</v>
@@ -3892,38 +3889,6 @@
         <v>0</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" ht="15" spans="1:10">
-      <c r="A108" s="1" t="n">
-        <v>813324</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/temp/diversos/Prensas.xlsx
+++ b/temp/diversos/Prensas.xlsx
@@ -73,9 +73,6 @@
     <t>BATENTE AGL AL100 A.EXT - BRUTO</t>
   </si>
   <si>
-    <t>BATENTE AGL MINI A.EXT - BRUTO</t>
-  </si>
-  <si>
     <t>BOBINA AÇO GALV. SAE1006 - 2,3 X 162MM</t>
   </si>
   <si>
@@ -142,6 +139,9 @@
     <t>BRACINHO ARTICULADO BV E NEW BV</t>
   </si>
   <si>
+    <t>BRACINHO ARTICULADO DZ HORIZONTAL</t>
+  </si>
+  <si>
     <t>CANTONEIRA SUPORTE FIX. BV E NEW BV - ZINCADA</t>
   </si>
   <si>
@@ -253,6 +253,9 @@
     <t>FUNDO PRETO PORTEIRO ELETRÔNICO COLETIVO 44 E 48 PONTOS</t>
   </si>
   <si>
+    <t>NI-RT SAE-060 AGL P16,8 04P</t>
+  </si>
+  <si>
     <t>NI-RT SAE-060 AGL P24 04P</t>
   </si>
   <si>
@@ -347,9 +350,6 @@
   </si>
   <si>
     <t>TAMPA DA FECHADURA ULTRA - PRETA</t>
-  </si>
-  <si>
-    <t>TRAVA MAIOR SUPORTE FX. DZ HORIZONTAL - ZINCADO</t>
   </si>
   <si>
     <t>TRAVAS DE ARTICULAÇÃO FIX. DZ HORIZONTAL - ZINCADO</t>
@@ -773,7 +773,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2274.902</v>
+        <v>2133.914</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -918,22 +918,22 @@
     </row>
     <row r="15" customHeight="1" ht="15" spans="1:10">
       <c r="A15" s="1" t="n">
-        <v>701014</v>
+        <v>201134</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1662</v>
+        <v>14466.896</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
     </row>
     <row r="16" customHeight="1" ht="15" spans="1:10">
       <c r="A16" s="1" t="n">
-        <v>201134</v>
+        <v>201149</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
@@ -965,7 +965,7 @@
         <v>7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>14466.896</v>
+        <v>2790.64</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0</v>
@@ -982,7 +982,7 @@
     </row>
     <row r="17" customHeight="1" ht="15" spans="1:10">
       <c r="A17" s="1" t="n">
-        <v>201149</v>
+        <v>208008</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>22</v>
@@ -997,7 +997,7 @@
         <v>7</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2790.64</v>
+        <v>445</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="18" customHeight="1" ht="15" spans="1:10">
       <c r="A18" s="1" t="n">
-        <v>208008</v>
+        <v>201002</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>23</v>
@@ -1029,7 +1029,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>445</v>
+        <v>5308.96</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="19" customHeight="1" ht="15" spans="1:10">
       <c r="A19" s="1" t="n">
-        <v>201002</v>
+        <v>201010</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>24</v>
@@ -1061,7 +1061,7 @@
         <v>7</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5840</v>
+        <v>11417.94</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="20" customHeight="1" ht="15" spans="1:10">
       <c r="A20" s="1" t="n">
-        <v>201010</v>
+        <v>201022</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>25</v>
@@ -1090,10 +1090,10 @@
         <v>6</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>11417.94</v>
+        <v>957.81008</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="21" customHeight="1" ht="15" spans="1:10">
       <c r="A21" s="1" t="n">
-        <v>201022</v>
+        <v>201078</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>26</v>
@@ -1122,10 +1122,10 @@
         <v>6</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>957.81008</v>
+        <v>14415.00775</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1142,7 +1142,7 @@
     </row>
     <row r="22" customHeight="1" ht="15" spans="1:10">
       <c r="A22" s="1" t="n">
-        <v>201078</v>
+        <v>201013</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>27</v>
@@ -1157,7 +1157,7 @@
         <v>7</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>14415.00775</v>
+        <v>3384.87175</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0</v>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="23" customHeight="1" ht="15" spans="1:10">
       <c r="A23" s="1" t="n">
-        <v>201013</v>
+        <v>201029</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>28</v>
@@ -1189,7 +1189,7 @@
         <v>7</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3384.87175</v>
+        <v>8010</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="24" customHeight="1" ht="15" spans="1:10">
       <c r="A24" s="1" t="n">
-        <v>201029</v>
+        <v>201003</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>29</v>
@@ -1221,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>8010</v>
+        <v>6548.896</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="25" customHeight="1" ht="15" spans="1:10">
       <c r="A25" s="1" t="n">
-        <v>201003</v>
+        <v>201001</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>30</v>
@@ -1253,7 +1253,7 @@
         <v>7</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>6905.28</v>
+        <v>5102.904948</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="26" customHeight="1" ht="15" spans="1:10">
       <c r="A26" s="1" t="n">
-        <v>201001</v>
+        <v>201131</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>31</v>
@@ -1285,7 +1285,7 @@
         <v>7</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5102.904948</v>
+        <v>596</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="27" customHeight="1" ht="15" spans="1:10">
       <c r="A27" s="1" t="n">
-        <v>201131</v>
+        <v>201085</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>32</v>
@@ -1317,7 +1317,7 @@
         <v>7</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>596</v>
+        <v>305.723</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="28" customHeight="1" ht="15" spans="1:10">
       <c r="A28" s="1" t="n">
-        <v>201085</v>
+        <v>201119</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>33</v>
@@ -1349,7 +1349,7 @@
         <v>7</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>305.723</v>
+        <v>3702</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="29" customHeight="1" ht="15" spans="1:10">
       <c r="A29" s="1" t="n">
-        <v>201119</v>
+        <v>201101</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>34</v>
@@ -1381,7 +1381,7 @@
         <v>7</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3702</v>
+        <v>1869.806032</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="30" customHeight="1" ht="15" spans="1:10">
       <c r="A30" s="1" t="n">
-        <v>201101</v>
+        <v>201023</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>35</v>
@@ -1410,10 +1410,10 @@
         <v>6</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1869.806032</v>
+        <v>1740.001836</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="31" customHeight="1" ht="15" spans="1:10">
       <c r="A31" s="1" t="n">
-        <v>201023</v>
+        <v>201025</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>36</v>
@@ -1445,7 +1445,7 @@
         <v>3</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1740.001836</v>
+        <v>3561.278306</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="32" customHeight="1" ht="15" spans="1:10">
       <c r="A32" s="1" t="n">
-        <v>201025</v>
+        <v>201007</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>37</v>
@@ -1474,10 +1474,10 @@
         <v>6</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3561.278306</v>
+        <v>6615</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="33" customHeight="1" ht="15" spans="1:10">
       <c r="A33" s="1" t="n">
-        <v>201007</v>
+        <v>201004</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>38</v>
@@ -1509,7 +1509,7 @@
         <v>7</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>6615</v>
+        <v>1181.28</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="34" customHeight="1" ht="15" spans="1:10">
       <c r="A34" s="1" t="n">
-        <v>201004</v>
+        <v>201015</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>39</v>
@@ -1541,7 +1541,7 @@
         <v>7</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1261.756</v>
+        <v>867.688038</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="35" customHeight="1" ht="15" spans="1:10">
       <c r="A35" s="1" t="n">
-        <v>201015</v>
+        <v>201005</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>40</v>
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1009.984269</v>
+        <v>1294.036985</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -1590,22 +1590,22 @@
     </row>
     <row r="36" customHeight="1" ht="15" spans="1:10">
       <c r="A36" s="1" t="n">
-        <v>201005</v>
+        <v>813292</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1294.036985</v>
+        <v>328</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="37" customHeight="1" ht="15" spans="1:10">
       <c r="A37" s="1" t="n">
-        <v>813292</v>
+        <v>813290</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>42</v>
@@ -1637,7 +1637,7 @@
         <v>3</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>328</v>
+        <v>200</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
         <v>46</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>14051</v>
+        <v>10206</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>3</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2534.693043</v>
+        <v>2392.89809</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0</v>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="74" customHeight="1" ht="15" spans="1:10">
       <c r="A74" s="1" t="n">
-        <v>813448</v>
+        <v>813442</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>80</v>
@@ -2821,7 +2821,7 @@
         <v>3</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2650</v>
+        <v>4032</v>
       </c>
       <c r="G74" s="3" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="75" customHeight="1" ht="15" spans="1:10">
       <c r="A75" s="1" t="n">
-        <v>813443</v>
+        <v>813448</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>81</v>
@@ -2853,7 +2853,7 @@
         <v>3</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2400</v>
+        <v>2650</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
     </row>
     <row r="76" customHeight="1" ht="15" spans="1:10">
       <c r="A76" s="1" t="n">
-        <v>813449</v>
+        <v>813443</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>82</v>
@@ -2885,7 +2885,7 @@
         <v>3</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>256</v>
+        <v>1200</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="77" customHeight="1" ht="15" spans="1:10">
       <c r="A77" s="1" t="n">
-        <v>401136</v>
+        <v>813449</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>83</v>
@@ -2917,7 +2917,7 @@
         <v>3</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>55582</v>
+        <v>256</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="78" customHeight="1" ht="15" spans="1:10">
       <c r="A78" s="1" t="n">
-        <v>707038</v>
+        <v>401136</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>84</v>
@@ -2949,7 +2949,7 @@
         <v>3</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>44637</v>
+        <v>55582</v>
       </c>
       <c r="G78" s="3" t="n">
         <v>0</v>
@@ -2966,7 +2966,7 @@
     </row>
     <row r="79" customHeight="1" ht="15" spans="1:10">
       <c r="A79" s="1" t="n">
-        <v>701050</v>
+        <v>707038</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>85</v>
@@ -2981,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>16720</v>
+        <v>44637</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0</v>
@@ -2998,22 +2998,22 @@
     </row>
     <row r="80" customHeight="1" ht="15" spans="1:10">
       <c r="A80" s="1" t="n">
-        <v>201099</v>
+        <v>701050</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>691.183</v>
+        <v>16720</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
     </row>
     <row r="81" customHeight="1" ht="15" spans="1:10">
       <c r="A81" s="1" t="n">
-        <v>201089</v>
+        <v>201099</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>87</v>
@@ -3045,7 +3045,7 @@
         <v>7</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>274.082</v>
+        <v>691.183</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="82" customHeight="1" ht="15" spans="1:10">
       <c r="A82" s="1" t="n">
-        <v>201040</v>
+        <v>201089</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>88</v>
@@ -3077,7 +3077,7 @@
         <v>7</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>235.98</v>
+        <v>274.082</v>
       </c>
       <c r="G82" s="3" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="83" customHeight="1" ht="15" spans="1:10">
       <c r="A83" s="1" t="n">
-        <v>201056</v>
+        <v>201040</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>89</v>
@@ -3109,7 +3109,7 @@
         <v>7</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>658.308</v>
+        <v>235.98</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="84" customHeight="1" ht="15" spans="1:10">
       <c r="A84" s="1" t="n">
-        <v>201057</v>
+        <v>201056</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>90</v>
@@ -3141,7 +3141,7 @@
         <v>7</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>107.69</v>
+        <v>658.308</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>0</v>
@@ -3158,7 +3158,7 @@
     </row>
     <row r="85" customHeight="1" ht="15" spans="1:10">
       <c r="A85" s="1" t="n">
-        <v>201095</v>
+        <v>201057</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>91</v>
@@ -3173,7 +3173,7 @@
         <v>7</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>233.362436</v>
+        <v>107.69</v>
       </c>
       <c r="G85" s="3" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     </row>
     <row r="86" customHeight="1" ht="15" spans="1:10">
       <c r="A86" s="1" t="n">
-        <v>201035</v>
+        <v>201095</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>92</v>
@@ -3202,10 +3202,10 @@
         <v>6</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>570.454147</v>
+        <v>233.362436</v>
       </c>
       <c r="G86" s="3" t="n">
         <v>0</v>
@@ -3222,22 +3222,22 @@
     </row>
     <row r="87" customHeight="1" ht="15" spans="1:10">
       <c r="A87" s="1" t="n">
-        <v>708014</v>
+        <v>201035</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>36271</v>
+        <v>570.454147</v>
       </c>
       <c r="G87" s="3" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="88" customHeight="1" ht="15" spans="1:10">
       <c r="A88" s="1" t="n">
-        <v>813286</v>
+        <v>708014</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>94</v>
@@ -3269,7 +3269,7 @@
         <v>3</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>6843</v>
+        <v>36271</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="89" customHeight="1" ht="15" spans="1:10">
       <c r="A89" s="1" t="n">
-        <v>708002</v>
+        <v>813286</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>95</v>
@@ -3301,7 +3301,7 @@
         <v>3</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>42074</v>
+        <v>6543</v>
       </c>
       <c r="G89" s="3" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="90" customHeight="1" ht="15" spans="1:10">
       <c r="A90" s="1" t="n">
-        <v>708001</v>
+        <v>708002</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>96</v>
@@ -3333,7 +3333,7 @@
         <v>3</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>25088</v>
+        <v>40698</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
     </row>
     <row r="91" customHeight="1" ht="15" spans="1:10">
       <c r="A91" s="1" t="n">
-        <v>412069</v>
+        <v>708001</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>97</v>
@@ -3365,7 +3365,7 @@
         <v>3</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>4000</v>
+        <v>23712</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0</v>
@@ -3382,7 +3382,7 @@
     </row>
     <row r="92" customHeight="1" ht="15" spans="1:10">
       <c r="A92" s="1" t="n">
-        <v>412044</v>
+        <v>412069</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>98</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="93" customHeight="1" ht="15" spans="1:10">
       <c r="A93" s="1" t="n">
-        <v>412057</v>
+        <v>412044</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>99</v>
@@ -3429,7 +3429,7 @@
         <v>3</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>400</v>
+        <v>5000</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="94" customHeight="1" ht="15" spans="1:10">
       <c r="A94" s="1" t="n">
-        <v>412088</v>
+        <v>412057</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>100</v>
@@ -3478,7 +3478,7 @@
     </row>
     <row r="95" customHeight="1" ht="15" spans="1:10">
       <c r="A95" s="1" t="n">
-        <v>412093</v>
+        <v>412088</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>101</v>
@@ -3493,7 +3493,7 @@
         <v>3</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>14000</v>
+        <v>400</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="96" customHeight="1" ht="15" spans="1:10">
       <c r="A96" s="1" t="n">
-        <v>412060</v>
+        <v>412093</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>102</v>
@@ -3525,7 +3525,7 @@
         <v>3</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>2500</v>
+        <v>12000</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
     </row>
     <row r="97" customHeight="1" ht="15" spans="1:10">
       <c r="A97" s="1" t="n">
-        <v>201117</v>
+        <v>412060</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>22809.378558</v>
+        <v>2500</v>
       </c>
       <c r="G97" s="3" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="98" customHeight="1" ht="15" spans="1:10">
       <c r="A98" s="1" t="n">
-        <v>201145</v>
+        <v>201117</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>104</v>
@@ -3589,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>3100</v>
+        <v>19896.698717</v>
       </c>
       <c r="G98" s="3" t="n">
         <v>0</v>
@@ -3606,7 +3606,7 @@
     </row>
     <row r="99" customHeight="1" ht="15" spans="1:10">
       <c r="A99" s="1" t="n">
-        <v>201127</v>
+        <v>201145</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>105</v>
@@ -3621,7 +3621,7 @@
         <v>7</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>698.4205</v>
+        <v>3100</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="100" customHeight="1" ht="15" spans="1:10">
       <c r="A100" s="1" t="n">
-        <v>201126</v>
+        <v>201127</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>106</v>
@@ -3653,7 +3653,7 @@
         <v>7</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>390</v>
+        <v>698.4205</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="101" customHeight="1" ht="15" spans="1:10">
       <c r="A101" s="1" t="n">
-        <v>201065</v>
+        <v>201126</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>107</v>
@@ -3685,7 +3685,7 @@
         <v>7</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>2712.33918</v>
+        <v>390</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="102" customHeight="1" ht="15" spans="1:10">
       <c r="A102" s="1" t="n">
-        <v>201066</v>
+        <v>201065</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>108</v>
@@ -3717,7 +3717,7 @@
         <v>7</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>11871.06</v>
+        <v>2712.33918</v>
       </c>
       <c r="G102" s="3" t="n">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="103" customHeight="1" ht="15" spans="1:10">
       <c r="A103" s="1" t="n">
-        <v>201051</v>
+        <v>201066</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>109</v>
@@ -3749,7 +3749,7 @@
         <v>7</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>3722</v>
+        <v>11871.06</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>0</v>
@@ -3766,22 +3766,22 @@
     </row>
     <row r="104" customHeight="1" ht="15" spans="1:10">
       <c r="A104" s="1" t="n">
-        <v>811762</v>
+        <v>201051</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>200</v>
+        <v>3722</v>
       </c>
       <c r="G104" s="3" t="n">
         <v>0</v>
@@ -3798,7 +3798,7 @@
     </row>
     <row r="105" customHeight="1" ht="15" spans="1:10">
       <c r="A105" s="1" t="n">
-        <v>801126</v>
+        <v>811762</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>111</v>
@@ -3813,7 +3813,7 @@
         <v>3</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="106" customHeight="1" ht="15" spans="1:10">
       <c r="A106" s="1" t="n">
-        <v>813325</v>
+        <v>801126</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>112</v>
@@ -3845,7 +3845,7 @@
         <v>3</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>3</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>100</v>
+        <v>1774</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>0</v>

--- a/temp/diversos/Prensas.xlsx
+++ b/temp/diversos/Prensas.xlsx
@@ -259,7 +259,7 @@
     <t>NI-RT SAE-060 AGL P24 04P</t>
   </si>
   <si>
-    <t>NI-RT SAE-060 AGL P27,6 04P</t>
+    <t>NI-RT SAE-060 AGL P33 04P</t>
   </si>
   <si>
     <t>NI-RT SAE-060 AGL P80 04P</t>
@@ -965,7 +965,7 @@
         <v>7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2790.64</v>
+        <v>1448.375</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
     </row>
     <row r="76" customHeight="1" ht="15" spans="1:10">
       <c r="A76" s="1" t="n">
-        <v>813443</v>
+        <v>813445</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>82</v>
@@ -2885,7 +2885,7 @@
         <v>3</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1200</v>
+        <v>1001</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>3</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0</v>
@@ -3589,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>19896.698717</v>
+        <v>13664.483172</v>
       </c>
       <c r="G98" s="3" t="n">
         <v>0</v>
